--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MISSISSIPPI_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MISSISSIPPI_2017.xlsx
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C75">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C158">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C380">
